--- a/tests/reports/unit_test_300_report.xlsx
+++ b/tests/reports/unit_test_300_report.xlsx
@@ -2885,7 +2885,7 @@
         <v>36</v>
       </c>
       <c r="J2" s="6">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>37</v>
@@ -2923,7 +2923,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="8">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>37</v>
@@ -2961,7 +2961,7 @@
         <v>50</v>
       </c>
       <c r="J4" s="6">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>37</v>
@@ -2999,7 +2999,7 @@
         <v>56</v>
       </c>
       <c r="J5" s="8">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>37</v>
@@ -3037,7 +3037,7 @@
         <v>36</v>
       </c>
       <c r="J6" s="6">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>37</v>
@@ -3075,7 +3075,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="8">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>37</v>
@@ -3113,7 +3113,7 @@
         <v>50</v>
       </c>
       <c r="J8" s="6">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>37</v>
@@ -3151,7 +3151,7 @@
         <v>56</v>
       </c>
       <c r="J9" s="8">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>37</v>
@@ -3189,7 +3189,7 @@
         <v>36</v>
       </c>
       <c r="J10" s="6">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>37</v>
@@ -3227,7 +3227,7 @@
         <v>44</v>
       </c>
       <c r="J11" s="8">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>37</v>
@@ -3265,7 +3265,7 @@
         <v>50</v>
       </c>
       <c r="J12" s="6">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>37</v>
@@ -3303,7 +3303,7 @@
         <v>56</v>
       </c>
       <c r="J13" s="8">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>37</v>
@@ -3341,7 +3341,7 @@
         <v>36</v>
       </c>
       <c r="J14" s="6">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>37</v>
@@ -3379,7 +3379,7 @@
         <v>44</v>
       </c>
       <c r="J15" s="8">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>37</v>
@@ -3417,7 +3417,7 @@
         <v>50</v>
       </c>
       <c r="J16" s="6">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>37</v>
@@ -3455,7 +3455,7 @@
         <v>56</v>
       </c>
       <c r="J17" s="8">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>37</v>
@@ -3493,7 +3493,7 @@
         <v>36</v>
       </c>
       <c r="J18" s="6">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>37</v>
@@ -3531,7 +3531,7 @@
         <v>44</v>
       </c>
       <c r="J19" s="8">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>37</v>
@@ -3569,7 +3569,7 @@
         <v>50</v>
       </c>
       <c r="J20" s="6">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>56</v>
       </c>
       <c r="J21" s="8">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>37</v>
@@ -3645,7 +3645,7 @@
         <v>36</v>
       </c>
       <c r="J22" s="6">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>37</v>
@@ -3683,7 +3683,7 @@
         <v>44</v>
       </c>
       <c r="J23" s="8">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>37</v>
@@ -3721,7 +3721,7 @@
         <v>50</v>
       </c>
       <c r="J24" s="6">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>37</v>
@@ -3759,7 +3759,7 @@
         <v>56</v>
       </c>
       <c r="J25" s="8">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>37</v>
@@ -3797,7 +3797,7 @@
         <v>36</v>
       </c>
       <c r="J26" s="6">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>37</v>
@@ -3835,7 +3835,7 @@
         <v>44</v>
       </c>
       <c r="J27" s="8">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>37</v>
@@ -3873,7 +3873,7 @@
         <v>50</v>
       </c>
       <c r="J28" s="6">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>37</v>
@@ -3911,7 +3911,7 @@
         <v>56</v>
       </c>
       <c r="J29" s="8">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>37</v>
@@ -3949,7 +3949,7 @@
         <v>36</v>
       </c>
       <c r="J30" s="6">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>37</v>
@@ -3987,7 +3987,7 @@
         <v>44</v>
       </c>
       <c r="J31" s="8">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>37</v>
@@ -4025,7 +4025,7 @@
         <v>50</v>
       </c>
       <c r="J32" s="6">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>37</v>
@@ -4063,7 +4063,7 @@
         <v>56</v>
       </c>
       <c r="J33" s="8">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="J34" s="6">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="K34" s="5" t="s">
         <v>37</v>
@@ -4139,7 +4139,7 @@
         <v>44</v>
       </c>
       <c r="J35" s="8">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>37</v>
@@ -4177,7 +4177,7 @@
         <v>50</v>
       </c>
       <c r="J36" s="6">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>37</v>
@@ -4215,7 +4215,7 @@
         <v>56</v>
       </c>
       <c r="J37" s="8">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>37</v>
@@ -4253,7 +4253,7 @@
         <v>36</v>
       </c>
       <c r="J38" s="6">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>37</v>
@@ -4291,7 +4291,7 @@
         <v>44</v>
       </c>
       <c r="J39" s="8">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>37</v>
@@ -4329,7 +4329,7 @@
         <v>50</v>
       </c>
       <c r="J40" s="6">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="K40" s="5" t="s">
         <v>37</v>
@@ -4367,7 +4367,7 @@
         <v>56</v>
       </c>
       <c r="J41" s="8">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>37</v>
@@ -4405,7 +4405,7 @@
         <v>36</v>
       </c>
       <c r="J42" s="6">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>37</v>
@@ -4443,7 +4443,7 @@
         <v>44</v>
       </c>
       <c r="J43" s="8">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>37</v>
@@ -4481,7 +4481,7 @@
         <v>50</v>
       </c>
       <c r="J44" s="6">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="K44" s="5" t="s">
         <v>37</v>
@@ -4519,7 +4519,7 @@
         <v>56</v>
       </c>
       <c r="J45" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>37</v>
@@ -4557,7 +4557,7 @@
         <v>36</v>
       </c>
       <c r="J46" s="6">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>44</v>
       </c>
       <c r="J47" s="8">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>37</v>
@@ -4633,7 +4633,7 @@
         <v>50</v>
       </c>
       <c r="J48" s="6">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="K48" s="5" t="s">
         <v>37</v>
@@ -4671,7 +4671,7 @@
         <v>56</v>
       </c>
       <c r="J49" s="8">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>37</v>
@@ -4709,7 +4709,7 @@
         <v>36</v>
       </c>
       <c r="J50" s="6">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="K50" s="5" t="s">
         <v>37</v>
@@ -4747,7 +4747,7 @@
         <v>44</v>
       </c>
       <c r="J51" s="8">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>37</v>
@@ -4785,7 +4785,7 @@
         <v>50</v>
       </c>
       <c r="J52" s="6">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="K52" s="5" t="s">
         <v>37</v>
@@ -4823,7 +4823,7 @@
         <v>56</v>
       </c>
       <c r="J53" s="8">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>37</v>
@@ -4861,7 +4861,7 @@
         <v>36</v>
       </c>
       <c r="J54" s="6">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="K54" s="5" t="s">
         <v>37</v>
@@ -4899,7 +4899,7 @@
         <v>44</v>
       </c>
       <c r="J55" s="8">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="K55" s="9" t="s">
         <v>37</v>
@@ -4937,7 +4937,7 @@
         <v>50</v>
       </c>
       <c r="J56" s="6">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K56" s="5" t="s">
         <v>37</v>
@@ -4975,7 +4975,7 @@
         <v>56</v>
       </c>
       <c r="J57" s="8">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>37</v>
@@ -5013,7 +5013,7 @@
         <v>36</v>
       </c>
       <c r="J58" s="6">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="K58" s="5" t="s">
         <v>37</v>
@@ -5051,7 +5051,7 @@
         <v>44</v>
       </c>
       <c r="J59" s="8">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>50</v>
       </c>
       <c r="J60" s="6">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="K60" s="5" t="s">
         <v>37</v>
@@ -5127,7 +5127,7 @@
         <v>56</v>
       </c>
       <c r="J61" s="8">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="K61" s="9" t="s">
         <v>37</v>
@@ -5165,7 +5165,7 @@
         <v>36</v>
       </c>
       <c r="J62" s="6">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="K62" s="5" t="s">
         <v>37</v>
@@ -5203,7 +5203,7 @@
         <v>44</v>
       </c>
       <c r="J63" s="8">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="K63" s="9" t="s">
         <v>37</v>
@@ -5241,7 +5241,7 @@
         <v>50</v>
       </c>
       <c r="J64" s="6">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="K64" s="5" t="s">
         <v>37</v>
@@ -5279,7 +5279,7 @@
         <v>56</v>
       </c>
       <c r="J65" s="8">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="K65" s="9" t="s">
         <v>37</v>
@@ -5317,7 +5317,7 @@
         <v>36</v>
       </c>
       <c r="J66" s="6">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K66" s="5" t="s">
         <v>37</v>
@@ -5355,7 +5355,7 @@
         <v>44</v>
       </c>
       <c r="J67" s="8">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="K67" s="9" t="s">
         <v>37</v>
@@ -5393,7 +5393,7 @@
         <v>50</v>
       </c>
       <c r="J68" s="6">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="K68" s="5" t="s">
         <v>37</v>
@@ -5431,7 +5431,7 @@
         <v>56</v>
       </c>
       <c r="J69" s="8">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="K69" s="9" t="s">
         <v>37</v>
@@ -5469,7 +5469,7 @@
         <v>36</v>
       </c>
       <c r="J70" s="6">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="K70" s="5" t="s">
         <v>37</v>
@@ -5507,7 +5507,7 @@
         <v>44</v>
       </c>
       <c r="J71" s="8">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="K71" s="9" t="s">
         <v>37</v>
@@ -5545,7 +5545,7 @@
         <v>50</v>
       </c>
       <c r="J72" s="6">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="K72" s="5" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>56</v>
       </c>
       <c r="J73" s="8">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="K73" s="9" t="s">
         <v>37</v>
@@ -5621,7 +5621,7 @@
         <v>36</v>
       </c>
       <c r="J74" s="6">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K74" s="5" t="s">
         <v>37</v>
@@ -5659,7 +5659,7 @@
         <v>44</v>
       </c>
       <c r="J75" s="8">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="K75" s="9" t="s">
         <v>37</v>
@@ -5697,7 +5697,7 @@
         <v>50</v>
       </c>
       <c r="J76" s="6">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="K76" s="5" t="s">
         <v>37</v>
@@ -5735,7 +5735,7 @@
         <v>56</v>
       </c>
       <c r="J77" s="8">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="K77" s="9" t="s">
         <v>37</v>
@@ -5773,7 +5773,7 @@
         <v>36</v>
       </c>
       <c r="J78" s="6">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="K78" s="5" t="s">
         <v>37</v>
@@ -5811,7 +5811,7 @@
         <v>44</v>
       </c>
       <c r="J79" s="8">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="K79" s="9" t="s">
         <v>37</v>
@@ -5849,7 +5849,7 @@
         <v>50</v>
       </c>
       <c r="J80" s="6">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="K80" s="5" t="s">
         <v>37</v>
@@ -5887,7 +5887,7 @@
         <v>56</v>
       </c>
       <c r="J81" s="8">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="K81" s="9" t="s">
         <v>37</v>
@@ -5925,7 +5925,7 @@
         <v>36</v>
       </c>
       <c r="J82" s="6">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="K82" s="5" t="s">
         <v>37</v>
@@ -5963,7 +5963,7 @@
         <v>44</v>
       </c>
       <c r="J83" s="8">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="K83" s="9" t="s">
         <v>37</v>
@@ -6001,7 +6001,7 @@
         <v>50</v>
       </c>
       <c r="J84" s="6">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="K84" s="5" t="s">
         <v>37</v>
@@ -6039,7 +6039,7 @@
         <v>56</v>
       </c>
       <c r="J85" s="8">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="K85" s="9" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="J86" s="6">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="K86" s="5" t="s">
         <v>37</v>
@@ -6115,7 +6115,7 @@
         <v>44</v>
       </c>
       <c r="J87" s="8">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="K87" s="9" t="s">
         <v>37</v>
@@ -6153,7 +6153,7 @@
         <v>50</v>
       </c>
       <c r="J88" s="6">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="K88" s="5" t="s">
         <v>37</v>
@@ -6191,7 +6191,7 @@
         <v>56</v>
       </c>
       <c r="J89" s="8">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K89" s="9" t="s">
         <v>37</v>
@@ -6229,7 +6229,7 @@
         <v>36</v>
       </c>
       <c r="J90" s="6">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K90" s="5" t="s">
         <v>37</v>
@@ -6267,7 +6267,7 @@
         <v>44</v>
       </c>
       <c r="J91" s="8">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="K91" s="9" t="s">
         <v>37</v>
@@ -6305,7 +6305,7 @@
         <v>50</v>
       </c>
       <c r="J92" s="6">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="K92" s="5" t="s">
         <v>37</v>
@@ -6343,7 +6343,7 @@
         <v>56</v>
       </c>
       <c r="J93" s="8">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="K93" s="9" t="s">
         <v>37</v>
@@ -6381,7 +6381,7 @@
         <v>36</v>
       </c>
       <c r="J94" s="6">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K94" s="5" t="s">
         <v>37</v>
@@ -6419,7 +6419,7 @@
         <v>44</v>
       </c>
       <c r="J95" s="8">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K95" s="9" t="s">
         <v>37</v>
@@ -6457,7 +6457,7 @@
         <v>50</v>
       </c>
       <c r="J96" s="6">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="K96" s="5" t="s">
         <v>37</v>
@@ -6495,7 +6495,7 @@
         <v>56</v>
       </c>
       <c r="J97" s="8">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="K97" s="9" t="s">
         <v>37</v>
@@ -6533,7 +6533,7 @@
         <v>36</v>
       </c>
       <c r="J98" s="6">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="K98" s="5" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>44</v>
       </c>
       <c r="J99" s="8">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="K99" s="9" t="s">
         <v>37</v>
@@ -6609,7 +6609,7 @@
         <v>50</v>
       </c>
       <c r="J100" s="6">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="K100" s="5" t="s">
         <v>37</v>
@@ -6647,7 +6647,7 @@
         <v>56</v>
       </c>
       <c r="J101" s="8">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="K101" s="9" t="s">
         <v>37</v>
@@ -6685,7 +6685,7 @@
         <v>36</v>
       </c>
       <c r="J102" s="6">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K102" s="5" t="s">
         <v>37</v>
@@ -6723,7 +6723,7 @@
         <v>44</v>
       </c>
       <c r="J103" s="8">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="K103" s="9" t="s">
         <v>37</v>
@@ -6761,7 +6761,7 @@
         <v>50</v>
       </c>
       <c r="J104" s="6">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="K104" s="5" t="s">
         <v>37</v>
@@ -6799,7 +6799,7 @@
         <v>56</v>
       </c>
       <c r="J105" s="8">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="K105" s="9" t="s">
         <v>37</v>
@@ -6837,7 +6837,7 @@
         <v>36</v>
       </c>
       <c r="J106" s="6">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="K106" s="5" t="s">
         <v>37</v>
@@ -6875,7 +6875,7 @@
         <v>44</v>
       </c>
       <c r="J107" s="8">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="K107" s="9" t="s">
         <v>37</v>
@@ -6913,7 +6913,7 @@
         <v>50</v>
       </c>
       <c r="J108" s="6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K108" s="5" t="s">
         <v>37</v>
@@ -6951,7 +6951,7 @@
         <v>56</v>
       </c>
       <c r="J109" s="8">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K109" s="9" t="s">
         <v>37</v>
@@ -6989,7 +6989,7 @@
         <v>36</v>
       </c>
       <c r="J110" s="6">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="K110" s="5" t="s">
         <v>37</v>
@@ -7027,7 +7027,7 @@
         <v>44</v>
       </c>
       <c r="J111" s="8">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="K111" s="9" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>50</v>
       </c>
       <c r="J112" s="6">
-        <v>72</v>
+        <v>147</v>
       </c>
       <c r="K112" s="5" t="s">
         <v>37</v>
@@ -7103,7 +7103,7 @@
         <v>56</v>
       </c>
       <c r="J113" s="8">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K113" s="9" t="s">
         <v>37</v>
@@ -7141,7 +7141,7 @@
         <v>36</v>
       </c>
       <c r="J114" s="6">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K114" s="5" t="s">
         <v>37</v>
@@ -7179,7 +7179,7 @@
         <v>44</v>
       </c>
       <c r="J115" s="8">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="K115" s="9" t="s">
         <v>37</v>
@@ -7217,7 +7217,7 @@
         <v>50</v>
       </c>
       <c r="J116" s="6">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K116" s="5" t="s">
         <v>37</v>
@@ -7255,7 +7255,7 @@
         <v>56</v>
       </c>
       <c r="J117" s="8">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K117" s="9" t="s">
         <v>37</v>
@@ -7293,7 +7293,7 @@
         <v>36</v>
       </c>
       <c r="J118" s="6">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="K118" s="5" t="s">
         <v>37</v>
@@ -7331,7 +7331,7 @@
         <v>44</v>
       </c>
       <c r="J119" s="8">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="K119" s="9" t="s">
         <v>37</v>
@@ -7369,7 +7369,7 @@
         <v>50</v>
       </c>
       <c r="J120" s="6">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="K120" s="5" t="s">
         <v>37</v>
@@ -7407,7 +7407,7 @@
         <v>56</v>
       </c>
       <c r="J121" s="8">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="K121" s="9" t="s">
         <v>37</v>
@@ -7445,7 +7445,7 @@
         <v>36</v>
       </c>
       <c r="J122" s="6">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="K122" s="5" t="s">
         <v>37</v>
@@ -7483,7 +7483,7 @@
         <v>44</v>
       </c>
       <c r="J123" s="8">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K123" s="9" t="s">
         <v>37</v>
@@ -7521,7 +7521,7 @@
         <v>50</v>
       </c>
       <c r="J124" s="6">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="K124" s="5" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>56</v>
       </c>
       <c r="J125" s="8">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K125" s="9" t="s">
         <v>37</v>
@@ -7597,7 +7597,7 @@
         <v>36</v>
       </c>
       <c r="J126" s="6">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="K126" s="5" t="s">
         <v>37</v>
@@ -7635,7 +7635,7 @@
         <v>44</v>
       </c>
       <c r="J127" s="8">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K127" s="9" t="s">
         <v>37</v>
@@ -7673,7 +7673,7 @@
         <v>50</v>
       </c>
       <c r="J128" s="6">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K128" s="5" t="s">
         <v>37</v>
@@ -7711,7 +7711,7 @@
         <v>56</v>
       </c>
       <c r="J129" s="8">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="K129" s="9" t="s">
         <v>37</v>
@@ -7749,7 +7749,7 @@
         <v>36</v>
       </c>
       <c r="J130" s="6">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="K130" s="5" t="s">
         <v>37</v>
@@ -7787,7 +7787,7 @@
         <v>44</v>
       </c>
       <c r="J131" s="8">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="K131" s="9" t="s">
         <v>37</v>
@@ -7825,7 +7825,7 @@
         <v>50</v>
       </c>
       <c r="J132" s="6">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="K132" s="5" t="s">
         <v>37</v>
@@ -7863,7 +7863,7 @@
         <v>56</v>
       </c>
       <c r="J133" s="8">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="K133" s="9" t="s">
         <v>37</v>
@@ -7901,7 +7901,7 @@
         <v>36</v>
       </c>
       <c r="J134" s="6">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="K134" s="5" t="s">
         <v>37</v>
@@ -7939,7 +7939,7 @@
         <v>44</v>
       </c>
       <c r="J135" s="8">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="K135" s="9" t="s">
         <v>37</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="J136" s="6">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="K136" s="5" t="s">
         <v>37</v>
@@ -8015,7 +8015,7 @@
         <v>56</v>
       </c>
       <c r="J137" s="8">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="K137" s="9" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="J138" s="6">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K138" s="5" t="s">
         <v>37</v>
@@ -8091,7 +8091,7 @@
         <v>44</v>
       </c>
       <c r="J139" s="8">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="K139" s="9" t="s">
         <v>37</v>
@@ -8129,7 +8129,7 @@
         <v>50</v>
       </c>
       <c r="J140" s="6">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K140" s="5" t="s">
         <v>37</v>
@@ -8167,7 +8167,7 @@
         <v>56</v>
       </c>
       <c r="J141" s="8">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="K141" s="9" t="s">
         <v>37</v>
@@ -8205,7 +8205,7 @@
         <v>36</v>
       </c>
       <c r="J142" s="6">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="K142" s="5" t="s">
         <v>37</v>
@@ -8243,7 +8243,7 @@
         <v>44</v>
       </c>
       <c r="J143" s="8">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="K143" s="9" t="s">
         <v>37</v>
@@ -8281,7 +8281,7 @@
         <v>50</v>
       </c>
       <c r="J144" s="6">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="K144" s="5" t="s">
         <v>37</v>
@@ -8319,7 +8319,7 @@
         <v>56</v>
       </c>
       <c r="J145" s="8">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="K145" s="9" t="s">
         <v>37</v>
@@ -8357,7 +8357,7 @@
         <v>36</v>
       </c>
       <c r="J146" s="6">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="K146" s="5" t="s">
         <v>37</v>
@@ -8395,7 +8395,7 @@
         <v>44</v>
       </c>
       <c r="J147" s="8">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="K147" s="9" t="s">
         <v>37</v>
@@ -8433,7 +8433,7 @@
         <v>50</v>
       </c>
       <c r="J148" s="6">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="K148" s="5" t="s">
         <v>37</v>
@@ -8471,7 +8471,7 @@
         <v>56</v>
       </c>
       <c r="J149" s="8">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="K149" s="9" t="s">
         <v>37</v>
@@ -8509,7 +8509,7 @@
         <v>36</v>
       </c>
       <c r="J150" s="6">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="K150" s="5" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>44</v>
       </c>
       <c r="J151" s="8">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K151" s="9" t="s">
         <v>37</v>
@@ -8585,7 +8585,7 @@
         <v>50</v>
       </c>
       <c r="J152" s="6">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="K152" s="5" t="s">
         <v>37</v>
@@ -8623,7 +8623,7 @@
         <v>56</v>
       </c>
       <c r="J153" s="8">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="K153" s="9" t="s">
         <v>37</v>
@@ -8661,7 +8661,7 @@
         <v>36</v>
       </c>
       <c r="J154" s="6">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K154" s="5" t="s">
         <v>37</v>
@@ -8699,7 +8699,7 @@
         <v>44</v>
       </c>
       <c r="J155" s="8">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="K155" s="9" t="s">
         <v>37</v>
@@ -8737,7 +8737,7 @@
         <v>50</v>
       </c>
       <c r="J156" s="6">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="K156" s="5" t="s">
         <v>37</v>
@@ -8775,7 +8775,7 @@
         <v>56</v>
       </c>
       <c r="J157" s="8">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="K157" s="9" t="s">
         <v>37</v>
@@ -8813,7 +8813,7 @@
         <v>36</v>
       </c>
       <c r="J158" s="6">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="K158" s="5" t="s">
         <v>37</v>
@@ -8851,7 +8851,7 @@
         <v>44</v>
       </c>
       <c r="J159" s="8">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="K159" s="9" t="s">
         <v>37</v>
@@ -8889,7 +8889,7 @@
         <v>50</v>
       </c>
       <c r="J160" s="6">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K160" s="5" t="s">
         <v>37</v>
@@ -8927,7 +8927,7 @@
         <v>56</v>
       </c>
       <c r="J161" s="8">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="K161" s="9" t="s">
         <v>37</v>
@@ -8965,7 +8965,7 @@
         <v>36</v>
       </c>
       <c r="J162" s="6">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="K162" s="5" t="s">
         <v>37</v>
@@ -9003,7 +9003,7 @@
         <v>44</v>
       </c>
       <c r="J163" s="8">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="K163" s="9" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>50</v>
       </c>
       <c r="J164" s="6">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="K164" s="5" t="s">
         <v>37</v>
@@ -9079,7 +9079,7 @@
         <v>56</v>
       </c>
       <c r="J165" s="8">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="K165" s="9" t="s">
         <v>37</v>
@@ -9117,7 +9117,7 @@
         <v>36</v>
       </c>
       <c r="J166" s="6">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="K166" s="5" t="s">
         <v>37</v>
@@ -9155,7 +9155,7 @@
         <v>44</v>
       </c>
       <c r="J167" s="8">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="K167" s="9" t="s">
         <v>37</v>
@@ -9193,7 +9193,7 @@
         <v>50</v>
       </c>
       <c r="J168" s="6">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="K168" s="5" t="s">
         <v>37</v>
@@ -9231,7 +9231,7 @@
         <v>56</v>
       </c>
       <c r="J169" s="8">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="K169" s="9" t="s">
         <v>37</v>
@@ -9269,7 +9269,7 @@
         <v>36</v>
       </c>
       <c r="J170" s="6">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="K170" s="5" t="s">
         <v>37</v>
@@ -9307,7 +9307,7 @@
         <v>44</v>
       </c>
       <c r="J171" s="8">
-        <v>144</v>
+        <v>87</v>
       </c>
       <c r="K171" s="9" t="s">
         <v>37</v>
@@ -9345,7 +9345,7 @@
         <v>50</v>
       </c>
       <c r="J172" s="6">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="K172" s="5" t="s">
         <v>37</v>
@@ -9383,7 +9383,7 @@
         <v>56</v>
       </c>
       <c r="J173" s="8">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="K173" s="9" t="s">
         <v>37</v>
@@ -9421,7 +9421,7 @@
         <v>36</v>
       </c>
       <c r="J174" s="6">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K174" s="5" t="s">
         <v>37</v>
@@ -9459,7 +9459,7 @@
         <v>44</v>
       </c>
       <c r="J175" s="8">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K175" s="9" t="s">
         <v>37</v>
@@ -9497,7 +9497,7 @@
         <v>50</v>
       </c>
       <c r="J176" s="6">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="K176" s="5" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>56</v>
       </c>
       <c r="J177" s="8">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="K177" s="9" t="s">
         <v>37</v>
@@ -9573,7 +9573,7 @@
         <v>36</v>
       </c>
       <c r="J178" s="6">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="K178" s="5" t="s">
         <v>37</v>
@@ -9611,7 +9611,7 @@
         <v>44</v>
       </c>
       <c r="J179" s="8">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="K179" s="9" t="s">
         <v>37</v>
@@ -9649,7 +9649,7 @@
         <v>50</v>
       </c>
       <c r="J180" s="6">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="K180" s="5" t="s">
         <v>37</v>
@@ -9687,7 +9687,7 @@
         <v>56</v>
       </c>
       <c r="J181" s="8">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="K181" s="9" t="s">
         <v>37</v>
@@ -9725,7 +9725,7 @@
         <v>36</v>
       </c>
       <c r="J182" s="6">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K182" s="5" t="s">
         <v>37</v>
@@ -9763,7 +9763,7 @@
         <v>44</v>
       </c>
       <c r="J183" s="8">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="K183" s="9" t="s">
         <v>37</v>
@@ -9801,7 +9801,7 @@
         <v>50</v>
       </c>
       <c r="J184" s="6">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="K184" s="5" t="s">
         <v>37</v>
@@ -9839,7 +9839,7 @@
         <v>56</v>
       </c>
       <c r="J185" s="8">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="K185" s="9" t="s">
         <v>37</v>
@@ -9877,7 +9877,7 @@
         <v>36</v>
       </c>
       <c r="J186" s="6">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K186" s="5" t="s">
         <v>37</v>
@@ -9915,7 +9915,7 @@
         <v>44</v>
       </c>
       <c r="J187" s="8">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="K187" s="9" t="s">
         <v>37</v>
@@ -9953,7 +9953,7 @@
         <v>50</v>
       </c>
       <c r="J188" s="6">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K188" s="5" t="s">
         <v>37</v>
@@ -9991,7 +9991,7 @@
         <v>56</v>
       </c>
       <c r="J189" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K189" s="9" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="J190" s="6">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="K190" s="5" t="s">
         <v>37</v>
@@ -10067,7 +10067,7 @@
         <v>44</v>
       </c>
       <c r="J191" s="8">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="K191" s="9" t="s">
         <v>37</v>
@@ -10105,7 +10105,7 @@
         <v>50</v>
       </c>
       <c r="J192" s="6">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="K192" s="5" t="s">
         <v>37</v>
@@ -10143,7 +10143,7 @@
         <v>56</v>
       </c>
       <c r="J193" s="8">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="K193" s="9" t="s">
         <v>37</v>
@@ -10181,7 +10181,7 @@
         <v>36</v>
       </c>
       <c r="J194" s="6">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="K194" s="5" t="s">
         <v>37</v>
@@ -10219,7 +10219,7 @@
         <v>44</v>
       </c>
       <c r="J195" s="8">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="K195" s="9" t="s">
         <v>37</v>
@@ -10257,7 +10257,7 @@
         <v>50</v>
       </c>
       <c r="J196" s="6">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K196" s="5" t="s">
         <v>37</v>
@@ -10295,7 +10295,7 @@
         <v>56</v>
       </c>
       <c r="J197" s="8">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="K197" s="9" t="s">
         <v>37</v>
@@ -10333,7 +10333,7 @@
         <v>36</v>
       </c>
       <c r="J198" s="6">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="K198" s="5" t="s">
         <v>37</v>
@@ -10371,7 +10371,7 @@
         <v>44</v>
       </c>
       <c r="J199" s="8">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="K199" s="9" t="s">
         <v>37</v>
@@ -10409,7 +10409,7 @@
         <v>50</v>
       </c>
       <c r="J200" s="6">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="K200" s="5" t="s">
         <v>37</v>
@@ -10485,7 +10485,7 @@
         <v>36</v>
       </c>
       <c r="J202" s="6">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="K202" s="5" t="s">
         <v>37</v>
@@ -10561,7 +10561,7 @@
         <v>50</v>
       </c>
       <c r="J204" s="6">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="K204" s="5" t="s">
         <v>37</v>
@@ -10599,7 +10599,7 @@
         <v>56</v>
       </c>
       <c r="J205" s="8">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="K205" s="9" t="s">
         <v>37</v>
@@ -10637,7 +10637,7 @@
         <v>36</v>
       </c>
       <c r="J206" s="6">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="K206" s="5" t="s">
         <v>37</v>
@@ -10675,7 +10675,7 @@
         <v>44</v>
       </c>
       <c r="J207" s="8">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="K207" s="9" t="s">
         <v>37</v>
@@ -10713,7 +10713,7 @@
         <v>50</v>
       </c>
       <c r="J208" s="6">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="K208" s="5" t="s">
         <v>37</v>
@@ -10751,7 +10751,7 @@
         <v>56</v>
       </c>
       <c r="J209" s="8">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="K209" s="9" t="s">
         <v>37</v>
@@ -10789,7 +10789,7 @@
         <v>36</v>
       </c>
       <c r="J210" s="6">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="K210" s="5" t="s">
         <v>37</v>
@@ -10827,7 +10827,7 @@
         <v>44</v>
       </c>
       <c r="J211" s="8">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="K211" s="9" t="s">
         <v>37</v>
@@ -10865,7 +10865,7 @@
         <v>50</v>
       </c>
       <c r="J212" s="6">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="K212" s="5" t="s">
         <v>37</v>
@@ -10903,7 +10903,7 @@
         <v>56</v>
       </c>
       <c r="J213" s="8">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="K213" s="9" t="s">
         <v>37</v>
@@ -10941,7 +10941,7 @@
         <v>36</v>
       </c>
       <c r="J214" s="6">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="K214" s="5" t="s">
         <v>37</v>
@@ -10979,7 +10979,7 @@
         <v>44</v>
       </c>
       <c r="J215" s="8">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="K215" s="9" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>50</v>
       </c>
       <c r="J216" s="6">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K216" s="5" t="s">
         <v>37</v>
@@ -11055,7 +11055,7 @@
         <v>56</v>
       </c>
       <c r="J217" s="8">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="K217" s="9" t="s">
         <v>37</v>
@@ -11093,7 +11093,7 @@
         <v>36</v>
       </c>
       <c r="J218" s="6">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="K218" s="5" t="s">
         <v>37</v>
@@ -11131,7 +11131,7 @@
         <v>44</v>
       </c>
       <c r="J219" s="8">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K219" s="9" t="s">
         <v>37</v>
@@ -11169,7 +11169,7 @@
         <v>50</v>
       </c>
       <c r="J220" s="6">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="K220" s="5" t="s">
         <v>37</v>
@@ -11207,7 +11207,7 @@
         <v>56</v>
       </c>
       <c r="J221" s="8">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K221" s="9" t="s">
         <v>37</v>
@@ -11245,7 +11245,7 @@
         <v>36</v>
       </c>
       <c r="J222" s="6">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="K222" s="5" t="s">
         <v>37</v>
@@ -11283,7 +11283,7 @@
         <v>44</v>
       </c>
       <c r="J223" s="8">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="K223" s="9" t="s">
         <v>37</v>
@@ -11321,7 +11321,7 @@
         <v>50</v>
       </c>
       <c r="J224" s="6">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K224" s="5" t="s">
         <v>37</v>
@@ -11359,7 +11359,7 @@
         <v>56</v>
       </c>
       <c r="J225" s="8">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="K225" s="9" t="s">
         <v>37</v>
@@ -11397,7 +11397,7 @@
         <v>36</v>
       </c>
       <c r="J226" s="6">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="K226" s="5" t="s">
         <v>37</v>
@@ -11435,7 +11435,7 @@
         <v>44</v>
       </c>
       <c r="J227" s="8">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="K227" s="9" t="s">
         <v>37</v>
@@ -11473,7 +11473,7 @@
         <v>50</v>
       </c>
       <c r="J228" s="6">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="K228" s="5" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>56</v>
       </c>
       <c r="J229" s="8">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K229" s="9" t="s">
         <v>37</v>
@@ -11549,7 +11549,7 @@
         <v>36</v>
       </c>
       <c r="J230" s="6">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="K230" s="5" t="s">
         <v>37</v>
@@ -11587,7 +11587,7 @@
         <v>44</v>
       </c>
       <c r="J231" s="8">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="K231" s="9" t="s">
         <v>37</v>
@@ -11625,7 +11625,7 @@
         <v>50</v>
       </c>
       <c r="J232" s="6">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="K232" s="5" t="s">
         <v>37</v>
@@ -11663,7 +11663,7 @@
         <v>56</v>
       </c>
       <c r="J233" s="8">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="K233" s="9" t="s">
         <v>37</v>
@@ -11701,7 +11701,7 @@
         <v>36</v>
       </c>
       <c r="J234" s="6">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="K234" s="5" t="s">
         <v>37</v>
@@ -11739,7 +11739,7 @@
         <v>44</v>
       </c>
       <c r="J235" s="8">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="K235" s="9" t="s">
         <v>37</v>
@@ -11777,7 +11777,7 @@
         <v>50</v>
       </c>
       <c r="J236" s="6">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="K236" s="5" t="s">
         <v>37</v>
@@ -11815,7 +11815,7 @@
         <v>56</v>
       </c>
       <c r="J237" s="8">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K237" s="9" t="s">
         <v>37</v>
@@ -11853,7 +11853,7 @@
         <v>36</v>
       </c>
       <c r="J238" s="6">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="K238" s="5" t="s">
         <v>37</v>
@@ -11929,7 +11929,7 @@
         <v>50</v>
       </c>
       <c r="J240" s="6">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="K240" s="5" t="s">
         <v>37</v>
@@ -11967,7 +11967,7 @@
         <v>56</v>
       </c>
       <c r="J241" s="8">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="K241" s="9" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="J242" s="6">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="K242" s="5" t="s">
         <v>37</v>
@@ -12043,7 +12043,7 @@
         <v>44</v>
       </c>
       <c r="J243" s="8">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K243" s="9" t="s">
         <v>37</v>
@@ -12081,7 +12081,7 @@
         <v>50</v>
       </c>
       <c r="J244" s="6">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="K244" s="5" t="s">
         <v>37</v>
@@ -12119,7 +12119,7 @@
         <v>56</v>
       </c>
       <c r="J245" s="8">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K245" s="9" t="s">
         <v>37</v>
@@ -12157,7 +12157,7 @@
         <v>36</v>
       </c>
       <c r="J246" s="6">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="K246" s="5" t="s">
         <v>37</v>
@@ -12195,7 +12195,7 @@
         <v>44</v>
       </c>
       <c r="J247" s="8">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="K247" s="9" t="s">
         <v>37</v>
@@ -12233,7 +12233,7 @@
         <v>50</v>
       </c>
       <c r="J248" s="6">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K248" s="5" t="s">
         <v>37</v>
@@ -12271,7 +12271,7 @@
         <v>56</v>
       </c>
       <c r="J249" s="8">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="K249" s="9" t="s">
         <v>37</v>
@@ -12309,7 +12309,7 @@
         <v>36</v>
       </c>
       <c r="J250" s="6">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K250" s="5" t="s">
         <v>37</v>
@@ -12347,7 +12347,7 @@
         <v>44</v>
       </c>
       <c r="J251" s="8">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="K251" s="9" t="s">
         <v>37</v>
@@ -12385,7 +12385,7 @@
         <v>50</v>
       </c>
       <c r="J252" s="6">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="K252" s="5" t="s">
         <v>37</v>
@@ -12423,7 +12423,7 @@
         <v>56</v>
       </c>
       <c r="J253" s="8">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="K253" s="9" t="s">
         <v>37</v>
@@ -12461,7 +12461,7 @@
         <v>36</v>
       </c>
       <c r="J254" s="6">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="K254" s="5" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>44</v>
       </c>
       <c r="J255" s="8">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="K255" s="9" t="s">
         <v>37</v>
@@ -12537,7 +12537,7 @@
         <v>50</v>
       </c>
       <c r="J256" s="6">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K256" s="5" t="s">
         <v>37</v>
@@ -12575,7 +12575,7 @@
         <v>56</v>
       </c>
       <c r="J257" s="8">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="K257" s="9" t="s">
         <v>37</v>
@@ -12613,7 +12613,7 @@
         <v>36</v>
       </c>
       <c r="J258" s="6">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c r="K258" s="5" t="s">
         <v>37</v>
@@ -12651,7 +12651,7 @@
         <v>44</v>
       </c>
       <c r="J259" s="8">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="K259" s="9" t="s">
         <v>37</v>
@@ -12689,7 +12689,7 @@
         <v>50</v>
       </c>
       <c r="J260" s="6">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="K260" s="5" t="s">
         <v>37</v>
@@ -12727,7 +12727,7 @@
         <v>56</v>
       </c>
       <c r="J261" s="8">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="K261" s="9" t="s">
         <v>37</v>
@@ -12765,7 +12765,7 @@
         <v>36</v>
       </c>
       <c r="J262" s="6">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="K262" s="5" t="s">
         <v>37</v>
@@ -12803,7 +12803,7 @@
         <v>44</v>
       </c>
       <c r="J263" s="8">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K263" s="9" t="s">
         <v>37</v>
@@ -12841,7 +12841,7 @@
         <v>50</v>
       </c>
       <c r="J264" s="6">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="K264" s="5" t="s">
         <v>37</v>
@@ -12879,7 +12879,7 @@
         <v>56</v>
       </c>
       <c r="J265" s="8">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="K265" s="9" t="s">
         <v>37</v>
@@ -12917,7 +12917,7 @@
         <v>36</v>
       </c>
       <c r="J266" s="6">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K266" s="5" t="s">
         <v>37</v>
@@ -12955,7 +12955,7 @@
         <v>44</v>
       </c>
       <c r="J267" s="8">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="K267" s="9" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>50</v>
       </c>
       <c r="J268" s="6">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="K268" s="5" t="s">
         <v>37</v>
@@ -13031,7 +13031,7 @@
         <v>56</v>
       </c>
       <c r="J269" s="8">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="K269" s="9" t="s">
         <v>37</v>
@@ -13069,7 +13069,7 @@
         <v>36</v>
       </c>
       <c r="J270" s="6">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="K270" s="5" t="s">
         <v>37</v>
@@ -13107,7 +13107,7 @@
         <v>44</v>
       </c>
       <c r="J271" s="8">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="K271" s="9" t="s">
         <v>37</v>
@@ -13145,7 +13145,7 @@
         <v>50</v>
       </c>
       <c r="J272" s="6">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K272" s="5" t="s">
         <v>37</v>
@@ -13183,7 +13183,7 @@
         <v>56</v>
       </c>
       <c r="J273" s="8">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="K273" s="9" t="s">
         <v>37</v>
@@ -13221,7 +13221,7 @@
         <v>36</v>
       </c>
       <c r="J274" s="6">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="K274" s="5" t="s">
         <v>37</v>
@@ -13259,7 +13259,7 @@
         <v>44</v>
       </c>
       <c r="J275" s="8">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="K275" s="9" t="s">
         <v>37</v>
@@ -13297,7 +13297,7 @@
         <v>50</v>
       </c>
       <c r="J276" s="6">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="K276" s="5" t="s">
         <v>37</v>
@@ -13335,7 +13335,7 @@
         <v>56</v>
       </c>
       <c r="J277" s="8">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="K277" s="9" t="s">
         <v>37</v>
@@ -13373,7 +13373,7 @@
         <v>36</v>
       </c>
       <c r="J278" s="6">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="K278" s="5" t="s">
         <v>37</v>
@@ -13411,7 +13411,7 @@
         <v>44</v>
       </c>
       <c r="J279" s="8">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="K279" s="9" t="s">
         <v>37</v>
@@ -13449,7 +13449,7 @@
         <v>50</v>
       </c>
       <c r="J280" s="6">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="K280" s="5" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>56</v>
       </c>
       <c r="J281" s="8">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="K281" s="9" t="s">
         <v>37</v>
@@ -13563,7 +13563,7 @@
         <v>44</v>
       </c>
       <c r="J283" s="8">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="K283" s="9" t="s">
         <v>37</v>
@@ -13601,7 +13601,7 @@
         <v>50</v>
       </c>
       <c r="J284" s="6">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="K284" s="5" t="s">
         <v>37</v>
@@ -13639,7 +13639,7 @@
         <v>56</v>
       </c>
       <c r="J285" s="8">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="K285" s="9" t="s">
         <v>37</v>
@@ -13677,7 +13677,7 @@
         <v>36</v>
       </c>
       <c r="J286" s="6">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="K286" s="5" t="s">
         <v>37</v>
@@ -13715,7 +13715,7 @@
         <v>44</v>
       </c>
       <c r="J287" s="8">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="K287" s="9" t="s">
         <v>37</v>
@@ -13753,7 +13753,7 @@
         <v>50</v>
       </c>
       <c r="J288" s="6">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="K288" s="5" t="s">
         <v>37</v>
@@ -13791,7 +13791,7 @@
         <v>56</v>
       </c>
       <c r="J289" s="8">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="K289" s="9" t="s">
         <v>37</v>
@@ -13829,7 +13829,7 @@
         <v>36</v>
       </c>
       <c r="J290" s="6">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="K290" s="5" t="s">
         <v>37</v>
@@ -13867,7 +13867,7 @@
         <v>44</v>
       </c>
       <c r="J291" s="8">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="K291" s="9" t="s">
         <v>37</v>
@@ -13905,7 +13905,7 @@
         <v>50</v>
       </c>
       <c r="J292" s="6">
-        <v>51</v>
+        <v>132</v>
       </c>
       <c r="K292" s="5" t="s">
         <v>37</v>
@@ -13943,7 +13943,7 @@
         <v>56</v>
       </c>
       <c r="J293" s="8">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="K293" s="9" t="s">
         <v>37</v>
@@ -13981,7 +13981,7 @@
         <v>36</v>
       </c>
       <c r="J294" s="6">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K294" s="5" t="s">
         <v>37</v>
@@ -14019,7 +14019,7 @@
         <v>44</v>
       </c>
       <c r="J295" s="8">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="K295" s="9" t="s">
         <v>37</v>
@@ -14057,7 +14057,7 @@
         <v>50</v>
       </c>
       <c r="J296" s="6">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="K296" s="5" t="s">
         <v>37</v>
@@ -14095,7 +14095,7 @@
         <v>56</v>
       </c>
       <c r="J297" s="8">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="K297" s="9" t="s">
         <v>37</v>
@@ -14133,7 +14133,7 @@
         <v>36</v>
       </c>
       <c r="J298" s="6">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="K298" s="5" t="s">
         <v>37</v>
@@ -14171,7 +14171,7 @@
         <v>44</v>
       </c>
       <c r="J299" s="8">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="K299" s="9" t="s">
         <v>37</v>
@@ -14209,7 +14209,7 @@
         <v>50</v>
       </c>
       <c r="J300" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="K300" s="5" t="s">
         <v>37</v>
@@ -14247,7 +14247,7 @@
         <v>56</v>
       </c>
       <c r="J301" s="8">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="K301" s="9" t="s">
         <v>37</v>
